--- a/report-2026-07-01.xlsx
+++ b/report-2026-07-01.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-01T19:13:42+05:30</t>
+    <t>Generated 2026-07-01T19:18:58+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-01T19:11:34+05:30 (2m7s ago)</t>
+    <t>2026-07-01T19:16:58+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>Last error</t>
@@ -495,10 +495,16 @@
     <t>19:11:34.407</t>
   </si>
   <si>
+    <t>2026-07-01T19:16:43.632136+05:30</t>
+  </si>
+  <si>
+    <t>19:16:43.632</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-01T19:13:42+05:30</t>
+    <t>2026-07-01T19:18:58+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1093,7 +1099,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 23s</t>
+          <t>0h 7m 39s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1113,7 +1119,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>88h 56m 9s</t>
+          <t>88h 57m 19s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1123,7 +1129,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:13:42</t>
+          <t>19:18:58</t>
         </is>
       </c>
     </row>
@@ -1180,17 +1186,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>74014.4</t>
+          <t>156689.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1200,7 +1206,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>339</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1220,7 +1226,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>88h 54m 44s</t>
+          <t>88h 57m 4s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1230,7 +1236,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:13:42</t>
+          <t>19:18:58</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1355,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-01T19:11:34.4076993+05:30</t>
+          <t>2026-07-01T19:16:43.632136+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1359,7 +1365,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19:11:34.407</t>
+          <t>19:16:43.632</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3794,18 +3800,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="s">
+    <row r="71">
+      <c r="A71" s="4">
+        <v>54</v>
+      </c>
+      <c r="B71" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C71" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E71" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J71" s="4">
+        <v>0</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
         <v>161</v>
       </c>
-      <c r="E72">
-        <v>53</v>
+      <c r="B73" t="s">
+        <v>162</v>
+      </c>
+      <c r="D73" t="s">
+        <v>163</v>
+      </c>
+      <c r="E73">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-01.xlsx
+++ b/report-2026-07-01.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-01T19:18:58+05:30</t>
+    <t>Generated 2026-07-01T19:24:01+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-01T19:16:58+05:30 (2m0s ago)</t>
+    <t>2026-07-01T19:22:01+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>5</t>
   </si>
   <si>
     <t>Last error</t>
@@ -501,10 +501,16 @@
     <t>19:16:43.632</t>
   </si>
   <si>
+    <t>2026-07-01T19:21:43.7165844+05:30</t>
+  </si>
+  <si>
+    <t>19:21:43.716</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-01T19:18:58+05:30</t>
+    <t>2026-07-01T19:24:01+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1099,7 +1105,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 39s</t>
+          <t>0h 12m 42s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1129,7 +1135,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>19:18:58</t>
+          <t>19:24:01</t>
         </is>
       </c>
     </row>
@@ -1186,17 +1192,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>156689.0</t>
+          <t>304631.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>7037</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1206,7 +1212,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>643</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1226,7 +1232,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>88h 57m 4s</t>
+          <t>88h 57m 19s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1236,7 +1242,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>19:18:58</t>
+          <t>19:24:01</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1361,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-01T19:16:43.632136+05:30</t>
+          <t>2026-07-01T19:21:43.7165844+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1365,7 +1371,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19:16:43.632</t>
+          <t>19:21:43.716</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3838,18 +3844,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="s">
+    <row r="72">
+      <c r="A72" s="4">
+        <v>55</v>
+      </c>
+      <c r="B72" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C72" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E72" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J72" s="4">
+        <v>0</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
         <v>163</v>
       </c>
-      <c r="E73">
-        <v>54</v>
+      <c r="B74" t="s">
+        <v>164</v>
+      </c>
+      <c r="D74" t="s">
+        <v>165</v>
+      </c>
+      <c r="E74">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
